--- a/RDC.F.xlsx
+++ b/RDC.F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4FC3B2-2A44-4551-BDB3-971607CA2B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0670334C-E542-40CB-8EC8-86B00B62C3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{5523CAF6-C60C-4F2C-8205-704482A319E3}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{5523CAF6-C60C-4F2C-8205-704482A319E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>87.86</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>1766.9831231400001</v>
+        <v>869.61473076000004</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>1901.0151231400002</v>
+        <v>1003.6467307600001</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">

--- a/RDC.F.xlsx
+++ b/RDC.F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0670334C-E542-40CB-8EC8-86B00B62C3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55E023D-28D4-4BF7-BF8B-152484EB35BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{5523CAF6-C60C-4F2C-8205-704482A319E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5523CAF6-C60C-4F2C-8205-704482A319E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>43.24</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>869.61473076000004</v>
+        <v>1333.3824387</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>1003.6467307600001</v>
+        <v>1467.4144387000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
